--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-diagnosis.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-diagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T13:39:17+00:00</t>
+    <t>2026-08-28T13:49:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-diagnosis.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-diagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T13:49:20+00:00</t>
+    <t>2026-08-28T14:00:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-diagnosis.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-diagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T14:00:29+00:00</t>
+    <t>2026-08-31T13:41:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-diagnosis.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-diagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T13:41:24+00:00</t>
+    <t>2026-09-02T03:14:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-diagnosis.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-diagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T03:14:53+00:00</t>
+    <t>2026-09-02T03:38:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-diagnosis.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-diagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T03:38:58+00:00</t>
+    <t>2026-09-02T04:00:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-diagnosis.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-diagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T06:41:45+00:00</t>
+    <t>2026-09-02T06:59:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-diagnosis.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-diagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T06:59:28+00:00</t>
+    <t>2026-09-02T09:29:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-diagnosis.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-diagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T09:29:03+00:00</t>
+    <t>2026-09-02T14:14:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -281,7 +281,7 @@
 con-4:If condition is abated, then clinicalStatus must be either inactive, resolved, or remission {abatement.empty() or clinicalStatus.coding.where(system='http://terminology.hl7.org/CodeSystem/condition-clinical' and (code='resolved' or code='remission' or code='inactive')).exists()}con-5:Condition.clinicalStatus SHALL NOT be present if verification Status is entered-in-error {verificationStatus.coding.where(system='http://terminology.hl7.org/CodeSystem/condition-ver-status' and code='entered-in-error').empty() or clinicalStatus.empty()}dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
-    <t>AnamneseUndDiagnostik.KlinischeDiagnose</t>
+    <t>anamneseUndDiagnostik.klinischeDiagnose</t>
   </si>
   <si>
     <t>Event</t>
@@ -730,7 +730,7 @@
 </t>
   </si>
   <si>
-    <t>AnamneseUndDiagnostik.KlinischeDiagnose.FeststellungsdatumKlinischeDia</t>
+    <t>anamneseUndDiagnostik.klinischeDiagnose.feststellungsdatumKlinischeDia</t>
   </si>
   <si>
     <t>Condition.modifierExtension</t>
@@ -1619,7 +1619,7 @@
     <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-seltene/ValueSet/mii-vs-seltene-hpo-phenotypic-observation-codes</t>
   </si>
   <si>
-    <t>AnamneseUndDiagnostik.Phaenotypisierung.HPOTerm</t>
+    <t>anamneseUndDiagnostik.phaenotypisierung.hpoTerm</t>
   </si>
   <si>
     <t>Condition.code.coding:hpo.id</t>
@@ -1890,7 +1890,7 @@
     <t>This will typically be the encounter the event occurred within, but some activities may be initiated prior to or after the official completion of an encounter but still be tied to the context of the encounter. This record indicates the encounter this particular record is associated with.  In the case of a "new" diagnosis reflecting ongoing/revised information about the condition, this might be distinct from the first encounter in which the underlying condition was first "known".</t>
   </si>
   <si>
-    <t>AnamneseUndDiagnostik.Untersuchungsdatum</t>
+    <t>anamneseUndDiagnostik.untersuchungsdatum</t>
   </si>
   <si>
     <t>Event.context</t>
@@ -1943,7 +1943,7 @@
     <t>closed</t>
   </si>
   <si>
-    <t>AnamneseUndDiagnostik.KlinischeDiagnose.AlterKlinischeDia</t>
+    <t>anamneseUndDiagnostik.klinischeDiagnose.alterKlinischeDia</t>
   </si>
   <si>
     <t>KlinischRelevanterZeitraum</t>
@@ -2801,7 +2801,7 @@
     <t>Links to other relevant information, including pathology reports.</t>
   </si>
   <si>
-    <t>AnamneseUndDiagnostik.Phaenotypisierung</t>
+    <t>anamneseUndDiagnostik.phaenotypisierung</t>
   </si>
   <si>
     <t>Condition.note</t>
@@ -3178,7 +3178,7 @@
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="61.125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="60.5390625" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="42.4375" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="25.4609375" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="255.0" customWidth="true" bestFit="true"/>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-diagnosis.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-diagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T14:14:40+00:00</t>
+    <t>2026-09-02T14:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1782,7 +1782,7 @@
     <t>Group is typically used for veterinary or public health use cases.</t>
   </si>
   <si>
-    <t>Patient</t>
+    <t>persoenlicheInfosIndexpatient</t>
   </si>
   <si>
     <t>Event.subject</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-diagnosis.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-diagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T14:33:43+00:00</t>
+    <t>2026-09-02T15:16:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-diagnosis.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-diagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T15:16:54+00:00</t>
+    <t>2026-09-02T16:13:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-diagnosis.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-diagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T16:13:05+00:00</t>
+    <t>2026-09-02T16:35:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-diagnosis.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-diagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T16:35:11+00:00</t>
+    <t>2026-09-02T16:52:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-diagnosis.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-diagnosis.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9988" uniqueCount="905">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9987" uniqueCount="905">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T16:52:58+00:00</t>
+    <t>2026-09-02T17:07:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1049,7 +1049,7 @@
     <t>The categorization is often highly contextual and may appear poorly differentiated or not very useful in other contexts.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-category|4.0.1</t>
+    <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-seltene/ValueSet/mii-vs-seltene-clinical-diagnosis-category</t>
   </si>
   <si>
     <t>&lt; 404684003 |Clinical finding|</t>
@@ -9773,9 +9773,7 @@
       <c r="X54" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="Y54" t="s" s="2">
-        <v>331</v>
-      </c>
+      <c r="Y54" s="2"/>
       <c r="Z54" t="s" s="2">
         <v>333</v>
       </c>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-diagnosis.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-diagnosis.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9987" uniqueCount="905">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9988" uniqueCount="905">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T17:07:58+00:00</t>
+    <t>2026-09-02T17:34:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1049,7 +1049,7 @@
     <t>The categorization is often highly contextual and may appear poorly differentiated or not very useful in other contexts.</t>
   </si>
   <si>
-    <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-seltene/ValueSet/mii-vs-seltene-clinical-diagnosis-category</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-category|4.0.1</t>
   </si>
   <si>
     <t>&lt; 404684003 |Clinical finding|</t>
@@ -9773,7 +9773,9 @@
       <c r="X54" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="Y54" s="2"/>
+      <c r="Y54" t="s" s="2">
+        <v>331</v>
+      </c>
       <c r="Z54" t="s" s="2">
         <v>333</v>
       </c>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-diagnosis.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-diagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T17:34:23+00:00</t>
+    <t>2026-09-02T17:52:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-diagnosis.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-diagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T17:52:03+00:00</t>
+    <t>2026-09-02T18:22:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-diagnosis.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-diagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T18:22:51+00:00</t>
+    <t>2026-09-03T06:59:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-diagnosis.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-diagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot</t>
+    <t>2027.0.0-ballot.rc1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T06:59:35+00:00</t>
+    <t>2026-09-03T07:17:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-diagnosis.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-diagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T07:17:59+00:00</t>
+    <t>2026-09-03T07:33:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-diagnosis.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-diagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T07:33:22+00:00</t>
+    <t>2026-09-03T09:08:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-diagnosis.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-diagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T09:08:22+00:00</t>
+    <t>2026-09-03T09:27:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-diagnosis.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-diagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T09:27:13+00:00</t>
+    <t>2026-09-03T09:44:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-diagnosis.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-clinical-diagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T09:44:41+00:00</t>
+    <t>2026-09-03T10:23:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
